--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142921</v>
+        <v>121142922</v>
       </c>
       <c r="B3" t="n">
-        <v>39842</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488069</v>
+        <v>488034</v>
       </c>
       <c r="R3" t="n">
-        <v>6540579</v>
+        <v>6540545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>121142924</v>
       </c>
       <c r="B4" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>121142923</v>
       </c>
       <c r="B5" t="n">
-        <v>97237</v>
+        <v>97247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142922</v>
+        <v>121142921</v>
       </c>
       <c r="B6" t="n">
-        <v>8421</v>
+        <v>39842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488034</v>
+        <v>488069</v>
       </c>
       <c r="R6" t="n">
-        <v>6540545</v>
+        <v>6540579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142922</v>
+        <v>121142923</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>97247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,32 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488034</v>
+        <v>488045</v>
       </c>
       <c r="R3" t="n">
-        <v>6540545</v>
+        <v>6540646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,18 +873,12 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142923</v>
+        <v>121142921</v>
       </c>
       <c r="B5" t="n">
-        <v>97247</v>
+        <v>39842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1023,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>214803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488045</v>
+        <v>488069</v>
       </c>
       <c r="R5" t="n">
-        <v>6540646</v>
+        <v>6540579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1094,18 @@
           <t>2023-10-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142921</v>
+        <v>121142922</v>
       </c>
       <c r="B6" t="n">
-        <v>39842</v>
+        <v>8421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488069</v>
+        <v>488034</v>
       </c>
       <c r="R6" t="n">
-        <v>6540579</v>
+        <v>6540545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142923</v>
+        <v>121142922</v>
       </c>
       <c r="B3" t="n">
-        <v>97247</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488045</v>
+        <v>488034</v>
       </c>
       <c r="R3" t="n">
-        <v>6540646</v>
+        <v>6540545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +874,18 @@
           <t>2023-10-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142924</v>
+        <v>121142923</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>97260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488031</v>
+        <v>488045</v>
       </c>
       <c r="R4" t="n">
-        <v>6540645</v>
+        <v>6540646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142921</v>
+        <v>121142924</v>
       </c>
       <c r="B5" t="n">
-        <v>39842</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,32 +1030,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488069</v>
+        <v>488031</v>
       </c>
       <c r="R5" t="n">
-        <v>6540579</v>
+        <v>6540645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,18 +1100,12 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142922</v>
+        <v>121142921</v>
       </c>
       <c r="B6" t="n">
-        <v>8421</v>
+        <v>39842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488034</v>
+        <v>488069</v>
       </c>
       <c r="R6" t="n">
-        <v>6540545</v>
+        <v>6540579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142922</v>
+        <v>121142921</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>39842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488034</v>
+        <v>488069</v>
       </c>
       <c r="R3" t="n">
-        <v>6540545</v>
+        <v>6540579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>121142923</v>
       </c>
       <c r="B4" t="n">
-        <v>97260</v>
+        <v>97261</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>121142924</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142921</v>
+        <v>121142922</v>
       </c>
       <c r="B6" t="n">
-        <v>39842</v>
+        <v>8421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488069</v>
+        <v>488034</v>
       </c>
       <c r="R6" t="n">
-        <v>6540579</v>
+        <v>6540545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142921</v>
+        <v>121142923</v>
       </c>
       <c r="B3" t="n">
-        <v>39842</v>
+        <v>97264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,32 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>214803</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488069</v>
+        <v>488045</v>
       </c>
       <c r="R3" t="n">
-        <v>6540579</v>
+        <v>6540646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,18 +873,12 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142923</v>
+        <v>121142924</v>
       </c>
       <c r="B4" t="n">
-        <v>97261</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488045</v>
+        <v>488031</v>
       </c>
       <c r="R4" t="n">
-        <v>6540646</v>
+        <v>6540645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142924</v>
+        <v>121142922</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>8424</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1023,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488031</v>
+        <v>488034</v>
       </c>
       <c r="R5" t="n">
-        <v>6540645</v>
+        <v>6540545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1094,18 @@
           <t>2023-10-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142922</v>
+        <v>121142921</v>
       </c>
       <c r="B6" t="n">
-        <v>8421</v>
+        <v>39845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488034</v>
+        <v>488069</v>
       </c>
       <c r="R6" t="n">
-        <v>6540545</v>
+        <v>6540579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142923</v>
+        <v>121142922</v>
       </c>
       <c r="B3" t="n">
-        <v>97264</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488045</v>
+        <v>488034</v>
       </c>
       <c r="R3" t="n">
-        <v>6540646</v>
+        <v>6540545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +874,18 @@
           <t>2023-10-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142924</v>
+        <v>121142923</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>97264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488031</v>
+        <v>488045</v>
       </c>
       <c r="R4" t="n">
-        <v>6540645</v>
+        <v>6540646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142922</v>
+        <v>121142921</v>
       </c>
       <c r="B5" t="n">
-        <v>8424</v>
+        <v>39845</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488034</v>
+        <v>488069</v>
       </c>
       <c r="R5" t="n">
-        <v>6540545</v>
+        <v>6540579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142921</v>
+        <v>121142924</v>
       </c>
       <c r="B6" t="n">
-        <v>39845</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,32 +1147,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488069</v>
+        <v>488031</v>
       </c>
       <c r="R6" t="n">
-        <v>6540579</v>
+        <v>6540645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,18 +1217,12 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112700474</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>121142922</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142923</v>
+        <v>121142921</v>
       </c>
       <c r="B4" t="n">
-        <v>97264</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,31 +905,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>214803</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488045</v>
+        <v>488069</v>
       </c>
       <c r="R4" t="n">
-        <v>6540646</v>
+        <v>6540579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +976,18 @@
           <t>2023-10-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142921</v>
+        <v>121142923</v>
       </c>
       <c r="B5" t="n">
-        <v>39845</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,32 +1017,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>214803</v>
+        <v>220250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488069</v>
+        <v>488045</v>
       </c>
       <c r="R5" t="n">
-        <v>6540579</v>
+        <v>6540646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,18 +1087,12 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,12 +1114,7 @@
         <v>121142924</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,6 +1213,111 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121142925</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6540717</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44863-2023 artfynd.xlsx
+++ b/artfynd/A 44863-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112700474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142922</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142921</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142924</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,8 +1348,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>